--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,64 +680,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96395506</v>
+        <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>102464</v>
+        <v>99270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221343</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AVK Norr, Nb</t>
+          <t>Ängesån, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>820979</v>
+        <v>821166</v>
       </c>
       <c r="R2" t="n">
-        <v>7421643</v>
+        <v>7421387</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,17 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vägnummer: 840, Väderstreck: Öster, Kommentar: &gt;100 individer, östra sidan</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,23 +767,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joseph Anderson, Björn Almkvist</t>
+          <t>Malin Schött</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -809,70 +789,59 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96395506</t>
+          <t>https://artportalen.se/Sighting/136936747</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96395507</v>
+        <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>102464</v>
+        <v>99257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221343</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>AVK Norr, Nb</t>
+          <t>Ängesån, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>821037</v>
+        <v>820999</v>
       </c>
       <c r="R3" t="n">
-        <v>7421562</v>
+        <v>7421611</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,17 +868,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Vägnummer: 840, Väderstreck: Öster, Kommentar: &gt;100 individer, östra sidan</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,23 +882,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joseph Anderson, Björn Almkvist</t>
+          <t>Malin Schött</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -944,70 +904,59 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96395507</t>
+          <t>https://artportalen.se/Sighting/136936743</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96395508</v>
+        <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>102464</v>
+        <v>99257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221343</v>
+        <v>220093</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>AVK Norr, Nb</t>
+          <t>Ängesån, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>821096</v>
+        <v>821002</v>
       </c>
       <c r="R4" t="n">
-        <v>7421481</v>
+        <v>7421608</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1034,17 +983,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Vägnummer: 840, Väderstreck: Öster, Kommentar: &gt;100 individer, östra sidan</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,23 +997,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joseph Anderson, Björn Almkvist</t>
+          <t>Malin Schött</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1079,66 +1019,62 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96395508</t>
+          <t>https://artportalen.se/Sighting/136936744</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>77436826</v>
+        <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>57791</v>
+        <v>99257</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102620</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rönsjärv Överkalix, Nb</t>
+          <t>Ängesån, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>852312</v>
+        <v>821105</v>
       </c>
       <c r="R5" t="n">
-        <v>7409518</v>
+        <v>7421467</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1162,22 +1098,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1186,71 +1112,84 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Ahlbäck</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Roger Ahlbäck</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77436826</t>
+          <t>https://artportalen.se/Sighting/136936745</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132267053</v>
+        <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99195</v>
+        <v>99257</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rönsjärv 16, Nb</t>
+          <t>Ängesån, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>851261</v>
+        <v>821145</v>
       </c>
       <c r="R6" t="n">
-        <v>7409078</v>
+        <v>7421414</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,12 +1213,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,84 +1227,95 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>lövrik, fuktig</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Malin Schött</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132267053</t>
+          <t>https://artportalen.se/Sighting/136936746</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114147069</v>
+        <v>96395506</v>
       </c>
       <c r="B7" t="n">
-        <v>93213</v>
+        <v>102464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>221343</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lansån 183, Nb</t>
+          <t>AVK Norr, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>831664</v>
+        <v>820979</v>
       </c>
       <c r="R7" t="n">
-        <v>7394545</v>
+        <v>7421643</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,12 +1339,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2021-01-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vägnummer: 840, Väderstreck: Öster, Kommentar: &gt;100 individer, östra sidan</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,85 +1358,99 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>äldre,100 år</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Joseph Anderson, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114147069</t>
+          <t>https://artportalen.se/Sighting/96395506</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113871021</v>
+        <v>96395507</v>
       </c>
       <c r="B8" t="n">
-        <v>90699</v>
+        <v>102464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>245044</v>
+        <v>221343</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>A.Riva</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lansån 130, Nb</t>
+          <t>AVK Norr, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>831849</v>
+        <v>821037</v>
       </c>
       <c r="R8" t="n">
-        <v>7394016</v>
+        <v>7421562</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,12 +1474,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2021-01-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Vägnummer: 840, Väderstreck: Öster, Kommentar: &gt;100 individer, östra sidan</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,44 +1493,42 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>äldre,100 år</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Joseph Anderson, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113871021</t>
+          <t>https://artportalen.se/Sighting/96395507</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112068770</v>
+        <v>96395508</v>
       </c>
       <c r="B9" t="n">
-        <v>58057</v>
+        <v>102464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,52 +1536,56 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>221343</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tväredet, Nb</t>
+          <t>AVK Norr, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>841085</v>
+        <v>821096</v>
       </c>
       <c r="R9" t="n">
-        <v>7389026</v>
+        <v>7421481</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1633,12 +1609,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2021-01-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2021-01-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vägnummer: 840, Väderstreck: Öster, Kommentar: &gt;100 individer, östra sidan</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,55 +1633,59 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Hedskog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rasmus Gabrielsson</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rasmus Gabrielsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Joseph Anderson, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112068770</t>
+          <t>https://artportalen.se/Sighting/96395508</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125732597</v>
+        <v>77436826</v>
       </c>
       <c r="B10" t="n">
-        <v>57602</v>
+        <v>57791</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100063</v>
+        <v>102620</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1712,23 +1697,23 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norra Sandsjärv, Nb</t>
+          <t>Rönsjärv Överkalix, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>842696</v>
+        <v>852312</v>
       </c>
       <c r="R10" t="n">
-        <v>7383660</v>
+        <v>7409518</v>
       </c>
       <c r="S10" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1752,22 +1737,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2019-04-30</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2019-04-30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,16 +1767,606 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Elfwing</t>
+          <t>Roger Ahlbäck</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Elfwing, Mia Ericsson, Therese Wåtz</t>
+          <t>Roger Ahlbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77436826</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132267053</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rönsjärv 16, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>851261</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7409078</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>lövrik, fuktig</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132267053</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114147069</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lansån 183, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>831664</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7394545</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>äldre,100 år</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114147069</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113871021</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90699</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>245044</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tallmusseron</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tricholoma roseoacerbum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>A.Riva</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lansån 130, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>831849</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7394016</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>äldre,100 år</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113871021</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>112068770</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tväredet, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>841085</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7389026</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Hedskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rasmus Gabrielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rasmus Gabrielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112068770</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125732597</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57602</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norra Sandsjärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>842696</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7383660</v>
+      </c>
+      <c r="S15" t="n">
+        <v>17</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Elfwing</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Elfwing, Mia Ericsson, Therese Wåtz</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125732597</t>
         </is>
@@ -1808,6 +2383,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1660,60 +1660,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>77436826</v>
+        <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>57791</v>
+        <v>102705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102620</v>
+        <v>221343</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rönsjärv Överkalix, Nb</t>
+          <t>Ängesån, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>852312</v>
+        <v>821050</v>
       </c>
       <c r="R10" t="n">
-        <v>7409518</v>
+        <v>7421553</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1737,22 +1729,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Öst och väst IS, sporadiskt spridda längst hela AVK. God förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,33 +1748,38 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Ahlbäck</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Ahlbäck</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Veronica Lindström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77436826</t>
+          <t>https://artportalen.se/Sighting/136950813</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132267053</v>
+        <v>77436826</v>
       </c>
       <c r="B11" t="n">
-        <v>99195</v>
+        <v>57791</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,37 +1787,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>102620</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hökuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Surnia ulula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rönsjärv 16, Nb</t>
+          <t>Rönsjärv Överkalix, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>851261</v>
+        <v>852312</v>
       </c>
       <c r="R11" t="n">
-        <v>7409078</v>
+        <v>7409518</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1849,12 +1853,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2019-04-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2019-04-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,41 +1879,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>lövrik, fuktig</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Roger Ahlbäck</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mariana Jussila Wahlberg</t>
+          <t>Roger Ahlbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132267053</t>
+          <t>https://artportalen.se/Sighting/77436826</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114147069</v>
+        <v>132267053</v>
       </c>
       <c r="B12" t="n">
-        <v>93213</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,37 +1911,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lansån 183, Nb</t>
+          <t>Rönsjärv 16, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>831664</v>
+        <v>851261</v>
       </c>
       <c r="R12" t="n">
-        <v>7394545</v>
+        <v>7409078</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,12 +1965,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,18 +1979,17 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Sandbarrskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>äldre,100 år</t>
+          <t>lövrik, fuktig</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2006,16 +2006,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114147069</t>
+          <t>https://artportalen.se/Sighting/132267053</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113871021</v>
+        <v>114147069</v>
       </c>
       <c r="B13" t="n">
-        <v>90699</v>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>245044</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma roseoacerbum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>A.Riva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2046,14 +2046,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lansån 130, Nb</t>
+          <t>Lansån 183, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>831849</v>
+        <v>831664</v>
       </c>
       <c r="R13" t="n">
-        <v>7394016</v>
+        <v>7394545</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2122,69 +2122,57 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113871021</t>
+          <t>https://artportalen.se/Sighting/114147069</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112068770</v>
+        <v>113871021</v>
       </c>
       <c r="B14" t="n">
-        <v>58057</v>
+        <v>90699</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>245044</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tallmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tricholoma roseoacerbum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>A.Riva</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tväredet, Nb</t>
+          <t>Lansån 130, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>841085</v>
+        <v>831849</v>
       </c>
       <c r="R14" t="n">
-        <v>7389026</v>
+        <v>7394016</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2208,12 +2196,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2222,88 +2210,97 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Hedskog</t>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>äldre,100 år</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rasmus Gabrielsson</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rasmus Gabrielsson</t>
+          <t>Mariana Jussila Wahlberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112068770</t>
+          <t>https://artportalen.se/Sighting/113871021</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125732597</v>
+        <v>112068770</v>
       </c>
       <c r="B15" t="n">
-        <v>57602</v>
+        <v>58057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100063</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norra Sandsjärv, Nb</t>
+          <t>Tväredet, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>842696</v>
+        <v>841085</v>
       </c>
       <c r="R15" t="n">
-        <v>7383660</v>
+        <v>7389026</v>
       </c>
       <c r="S15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2327,22 +2324,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,20 +2340,149 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Hedskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Elfwing</t>
+          <t>Rasmus Gabrielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Elfwing, Mia Ericsson, Therese Wåtz</t>
+          <t>Rasmus Gabrielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112068770</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125732597</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57602</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100063</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Smålom</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Gavia stellata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norra Sandsjärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>842696</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7383660</v>
+      </c>
+      <c r="S16" t="n">
+        <v>17</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Elfwing</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Elfwing, Mia Ericsson, Therese Wåtz</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125732597</t>
         </is>
@@ -2388,6 +2504,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99257</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99257</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99257</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99257</v>
+        <v>99263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99263</v>
+        <v>99265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99265</v>
+        <v>99266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99266</v>
+        <v>99272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99266</v>
+        <v>99272</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99266</v>
+        <v>99272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99266</v>
+        <v>99272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99272</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99272</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99272</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99272</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99280</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99278</v>
+        <v>99280</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99280</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99280</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99280</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99280</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99295</v>
+        <v>99298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99295</v>
+        <v>99298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99295</v>
+        <v>99298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99295</v>
+        <v>99298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99298</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99298</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99298</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99298</v>
+        <v>99308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99308</v>
+        <v>99309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99308</v>
+        <v>99309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99308</v>
+        <v>99309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99309</v>
+        <v>99314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99309</v>
+        <v>99314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99309</v>
+        <v>99314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99309</v>
+        <v>99314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99314</v>
+        <v>99316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99314</v>
+        <v>99316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99314</v>
+        <v>99316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99314</v>
+        <v>99316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99316</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99316</v>
+        <v>99322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99316</v>
+        <v>99322</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99316</v>
+        <v>99322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99322</v>
+        <v>99334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99322</v>
+        <v>99334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99322</v>
+        <v>99334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99334</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99334</v>
+        <v>99335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99334</v>
+        <v>99335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99334</v>
+        <v>99335</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99335</v>
+        <v>99338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99335</v>
+        <v>99338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99338</v>
+        <v>99339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99338</v>
+        <v>99339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99338</v>
+        <v>99339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99338</v>
+        <v>99339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 177-2023 artfynd.xlsx
+++ b/artfynd/S 177-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136936747</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136936743</v>
       </c>
       <c r="B3" t="n">
-        <v>99339</v>
+        <v>99342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136936744</v>
       </c>
       <c r="B4" t="n">
-        <v>99339</v>
+        <v>99342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136936745</v>
       </c>
       <c r="B5" t="n">
-        <v>99339</v>
+        <v>99342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136936746</v>
       </c>
       <c r="B6" t="n">
-        <v>99339</v>
+        <v>99342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136950813</v>
       </c>
       <c r="B10" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
